--- a/SHINHWA_QMS_WORKFLOW/01_ORIGINAL/MASTER_REF/품질경영매뉴얼 조직도.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/01_ORIGINAL/MASTER_REF/품질경영매뉴얼 조직도.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\q\SHINHWA_QMS_WORKFLOW\01_ORIGINAL\MASTER_REF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FC46522-663C-4812-B7E7-60CFA500232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6628D0-32F9-4C48-B248-44D51E9E2EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61AB2FED-B057-42BC-BAC2-0D348359DF43}"/>
+    <workbookView xWindow="11310" yWindow="3345" windowWidth="16125" windowHeight="10830" xr2:uid="{61AB2FED-B057-42BC-BAC2-0D348359DF43}"/>
   </bookViews>
   <sheets>
     <sheet name="조직도" sheetId="1" r:id="rId1"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>박철호부장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>직무</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -289,6 +285,10 @@
   </si>
   <si>
     <t xml:space="preserve">최형진 사원 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박철호 부장</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1668,48 +1668,48 @@
         <v>21</v>
       </c>
       <c r="AM21" s="32" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AN21" s="33"/>
     </row>
     <row r="22" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H22" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="41" t="s">
         <v>23</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>24</v>
       </c>
       <c r="J22" s="42"/>
       <c r="K22" s="43"/>
       <c r="N22" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O22" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P22" s="42"/>
       <c r="Q22" s="43"/>
       <c r="T22" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U22" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V22" s="44"/>
       <c r="W22" s="45"/>
       <c r="Z22" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA22" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB22" s="44"/>
       <c r="AC22" s="45"/>
       <c r="AF22" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG22" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH22" s="44"/>
       <c r="AI22" s="45"/>
@@ -1739,10 +1739,10 @@
       <c r="AH23" s="54"/>
       <c r="AI23" s="55"/>
       <c r="AL23" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM23" s="56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN23" s="57"/>
     </row>
@@ -1822,20 +1822,20 @@
       <c r="AG28" s="23"/>
       <c r="AH28" s="22"/>
       <c r="AL28" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM28" s="69" t="s">
         <v>30</v>
-      </c>
-      <c r="AM28" s="69" t="s">
-        <v>31</v>
       </c>
       <c r="AN28" s="70"/>
     </row>
     <row r="29" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H29" s="71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="72"/>
       <c r="J29" s="73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" s="74"/>
       <c r="R29" s="16"/>
@@ -1851,10 +1851,10 @@
       <c r="AG29" s="23"/>
       <c r="AH29" s="22"/>
       <c r="AL29" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AM29" s="56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN29" s="57"/>
     </row>
@@ -1874,36 +1874,36 @@
     </row>
     <row r="31" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H31" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="41" t="s">
         <v>23</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>24</v>
       </c>
       <c r="J31" s="44"/>
       <c r="K31" s="45"/>
       <c r="Q31" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R31" s="27"/>
       <c r="S31" s="28"/>
       <c r="U31" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V31" s="27"/>
       <c r="W31" s="28"/>
       <c r="Y31" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z31" s="27"/>
       <c r="AA31" s="28"/>
       <c r="AC31" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD31" s="27"/>
       <c r="AE31" s="28"/>
       <c r="AF31" s="23"/>
       <c r="AG31" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AH31" s="27"/>
       <c r="AI31" s="28"/>
@@ -1943,7 +1943,7 @@
         <v>21</v>
       </c>
       <c r="R33" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S33" s="33"/>
       <c r="T33" s="84"/>
@@ -1951,7 +1951,7 @@
         <v>21</v>
       </c>
       <c r="V33" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W33" s="33"/>
       <c r="X33" s="84"/>
@@ -1959,28 +1959,28 @@
         <v>21</v>
       </c>
       <c r="Z33" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA33" s="33"/>
       <c r="AC33" s="85" t="s">
         <v>21</v>
       </c>
       <c r="AD33" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AE33" s="33"/>
       <c r="AG33" s="85" t="s">
         <v>21</v>
       </c>
       <c r="AH33" s="32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI33" s="33"/>
       <c r="AL33" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM33" s="69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AN33" s="70"/>
     </row>
@@ -2001,47 +2001,47 @@
       <c r="AH34" s="87"/>
       <c r="AI34" s="88"/>
       <c r="AL34" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AM34" s="89" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AN34" s="90"/>
     </row>
     <row r="35" spans="8:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q35" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R35" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S35" s="57"/>
       <c r="U35" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V35" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W35" s="57"/>
       <c r="Y35" s="40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z35" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA35" s="91"/>
       <c r="AC35" s="92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD35" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE35" s="43"/>
       <c r="AG35" s="93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH35" s="56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AI35" s="57"/>
       <c r="AL35" s="81"/>
@@ -2097,81 +2097,81 @@
       <c r="V39" s="24"/>
       <c r="Z39" s="24"/>
       <c r="AC39" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD39" s="69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AE39" s="70"/>
       <c r="AH39" s="24"/>
     </row>
     <row r="40" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q40" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R40" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S40" s="70"/>
       <c r="U40" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V40" s="69" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W40" s="70"/>
       <c r="Y40" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z40" s="69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA40" s="70"/>
       <c r="AC40" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AD40" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE40" s="43"/>
       <c r="AG40" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH40" s="69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AI40" s="70"/>
     </row>
     <row r="41" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q41" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R41" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S41" s="91"/>
       <c r="U41" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V41" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W41" s="43"/>
       <c r="Y41" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z41" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA41" s="91"/>
       <c r="AC41" s="81"/>
       <c r="AD41" s="50"/>
       <c r="AE41" s="52"/>
       <c r="AG41" s="104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AH41" s="56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AI41" s="57"/>
     </row>
@@ -2210,19 +2210,19 @@
     </row>
     <row r="44" spans="8:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AC44" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD44" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AE44" s="70"/>
     </row>
     <row r="45" spans="8:40" x14ac:dyDescent="0.3">
       <c r="AC45" s="75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AD45" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE45" s="43"/>
     </row>
